--- a/Sample_run/1/student/DuyCNHE187327/OverallSummary.xlsx
+++ b/Sample_run/1/student/DuyCNHE187327/OverallSummary.xlsx
@@ -55,7 +55,7 @@
     <x:t>TC4</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 4 FAIL (ALL-OR-NOTHING), 7 PASS</x:t>
+    <x:t>Network flows: 3 FAIL (ALL-OR-NOTHING), 8 PASS</x:t>
   </x:si>
   <x:si>
     <x:t>TC5</x:t>
@@ -64,7 +64,7 @@
     <x:t>TC6</x:t>
   </x:si>
   <x:si>
-    <x:t>Network flows: 7 FAIL (ALL-OR-NOTHING), 15 PASS</x:t>
+    <x:t>Network flows: 9 FAIL (ALL-OR-NOTHING), 13 PASS</x:t>
   </x:si>
 </x:sst>
 </file>
